--- a/coleta_lay2x0_aovivo.xlsx
+++ b/coleta_lay2x0_aovivo.xlsx
@@ -580,11 +580,15 @@
           <t>RF</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
-        <v>96.40000000000001</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>10.5</v>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>96.4</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
       </c>
       <c r="I2" s="4" t="inlineStr"/>
       <c r="J2" s="4" t="inlineStr"/>
@@ -629,11 +633,15 @@
           <t>RF</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>8.4</v>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
       </c>
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr"/>
@@ -678,11 +686,15 @@
           <t>RF</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n">
-        <v>95.3</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>10.5</v>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>95.3</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
       </c>
       <c r="I4" s="4" t="inlineStr"/>
       <c r="J4" s="4" t="inlineStr"/>
